--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="406">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -684,108 +684,6 @@
     <t>Folate [Mass/volume] in Serum or Plasma</t>
   </si>
   <si>
-    <t>19177-5</t>
-  </si>
-  <si>
-    <t>Alpha-1-fetoprotein [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2039-6</t>
-  </si>
-  <si>
-    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2857-1</t>
-  </si>
-  <si>
-    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>19199-9</t>
-  </si>
-  <si>
-    <t>10886-0</t>
-  </si>
-  <si>
-    <t>Prostate specific Ag.free [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>97149-9</t>
-  </si>
-  <si>
-    <t>[-2]pro-prostate specific antigen [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>97150-7</t>
-  </si>
-  <si>
-    <t>Prostate Health Index in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>10334-1</t>
-  </si>
-  <si>
-    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>83082-8</t>
-  </si>
-  <si>
-    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>83085-1</t>
-  </si>
-  <si>
-    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>24108-3</t>
-  </si>
-  <si>
-    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>83084-4</t>
-  </si>
-  <si>
-    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>83083-6</t>
-  </si>
-  <si>
-    <t>Cancer Ag 15-3 [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>83112-3</t>
-  </si>
-  <si>
-    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>1834-1</t>
-  </si>
-  <si>
-    <t>9679-2</t>
-  </si>
-  <si>
-    <t>Squamous cell carcinoma Ag [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>19113-0</t>
-  </si>
-  <si>
-    <t>IgE [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>9633-9</t>
-  </si>
-  <si>
-    <t>Epstein Barr virus VCA IgA Ab [Presence] in Serum</t>
-  </si>
-  <si>
     <t>5196-1</t>
   </si>
   <si>
@@ -1221,42 +1119,6 @@
     <t>Epithelial cells [#/area] in Urine sediment by Microscopy high power field</t>
   </si>
   <si>
-    <t>10835-7</t>
-  </si>
-  <si>
-    <t>Lipoprotein A [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1869-7</t>
-  </si>
-  <si>
-    <t>Apolipoprotein A-I [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1884-6</t>
-  </si>
-  <si>
-    <t>Apolipoprotein B [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>33762-6</t>
-  </si>
-  <si>
-    <t>Natriuretic peptide.proB-type N-terminal [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>42254-3</t>
-  </si>
-  <si>
-    <t>Nuclear Ab [Presence] in Serum by Immunofluorescence</t>
-  </si>
-  <si>
-    <t>11572-5</t>
-  </si>
-  <si>
-    <t>Rheumatoid factor [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
     <t>1988-5</t>
   </si>
   <si>
@@ -1287,12 +1149,6 @@
     <t>Hemoglobin H/Hemoglobin.total in Blood</t>
   </si>
   <si>
-    <t>25390-6</t>
-  </si>
-  <si>
-    <t>CYFRA 21-1 [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
     <t>19876-2</t>
   </si>
   <si>
@@ -1302,7 +1158,13 @@
     <t>19868-9</t>
   </si>
   <si>
-    <t>Forced expiratory volume in 1 second</t>
+    <t>Forced vital capacity [Volume] Respiratory system by Spirometry</t>
+  </si>
+  <si>
+    <t>20150-9</t>
+  </si>
+  <si>
+    <t>Forced expiratory volume in 1 second [Volume] in Airways by Spirometry</t>
   </si>
   <si>
     <t>19926-5</t>
@@ -1640,7 +1502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B196"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2468,156 +2330,156 @@
         <v>229</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>224</v>
+        <v>252</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>266</v>
@@ -2625,18 +2487,18 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="125">
@@ -2660,196 +2522,196 @@
         <v>275</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>278</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>317</v>
@@ -2857,18 +2719,18 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B152" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B153" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="154">
@@ -2884,327 +2746,327 @@
         <v>324</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>402</v>
+        <v>22</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>403</v>
+        <v>22</v>
       </c>
     </row>
     <row r="196">
@@ -3213,198 +3075,6 @@
       </c>
       <c r="B196" t="s" s="2">
         <v>405</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="B204" t="s" s="2">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="B205" t="s" s="2">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="B206" t="s" s="2">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="B208" t="s" s="2">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="B209" t="s" s="2">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="B210" t="s" s="2">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B211" t="s" s="2">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="B212" t="s" s="2">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B213" t="s" s="2">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="B214" t="s" s="2">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="B215" t="s" s="2">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="B216" t="s" s="2">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B217" t="s" s="2">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="B218" t="s" s="2">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B219" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="B220" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,13 +114,13 @@
     <t>35200-5</t>
   </si>
   <si>
-    <t>Cholesterol [Mass/volume] in Blood</t>
+    <t>Cholesterol [Mass or Moles/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>1558-6</t>
   </si>
   <si>
-    <t>Fasting Glucose [Mass/volume] in Serum or Plasma</t>
+    <t>Fasting glucose [Mass/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>2339-0</t>
@@ -132,7 +132,7 @@
     <t>2345-7</t>
   </si>
   <si>
-    <t>Glucose [Mass/volume] in Serum or Plasma -- post fasting</t>
+    <t>Glucose [Mass/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>2571-8</t>
@@ -153,27 +153,24 @@
     <t>Cholesterol in HDL [Mass/volume] in Serum or Plasma</t>
   </si>
   <si>
-    <t>3048-6</t>
-  </si>
-  <si>
-    <t>Cholesterol in HDL [Mass/volume] in Blood</t>
-  </si>
-  <si>
     <t>2089-1</t>
   </si>
   <si>
+    <t>Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>13457-7</t>
+  </si>
+  <si>
+    <t>Cholesterol in LDL [Mass/volume] in Serum or Plasma by calculation</t>
+  </si>
+  <si>
+    <t>18262-6</t>
+  </si>
+  <si>
     <t>Cholesterol in LDL [Mass/volume] in Serum or Plasma by Direct assay</t>
   </si>
   <si>
-    <t>13457-7</t>
-  </si>
-  <si>
-    <t>Cholesterol in LDL [Mass/volume] in Serum or Plasma by calculation</t>
-  </si>
-  <si>
-    <t>18262-6</t>
-  </si>
-  <si>
     <t>2160-0</t>
   </si>
   <si>
@@ -195,40 +192,43 @@
     <t>5804-0</t>
   </si>
   <si>
-    <t>Protein [Presence] in Urine by Test strip</t>
+    <t>Protein [Mass/volume] in Urine by Test strip</t>
   </si>
   <si>
     <t>57735-3</t>
   </si>
   <si>
+    <t>Protein [Presence] in Urine by Automated test strip</t>
+  </si>
+  <si>
     <t>5196-1</t>
   </si>
   <si>
+    <t>Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>5195-3</t>
+  </si>
+  <si>
     <t>Hepatitis B virus surface Ag [Presence] in Serum</t>
   </si>
   <si>
-    <t>22326-3</t>
-  </si>
-  <si>
-    <t>Hepatitis B virus surface Ag [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
     <t>63557-3</t>
   </si>
   <si>
-    <t>Hepatitis B virus surface Ag [Presence] in Serum or Plasma by Immunoassay</t>
+    <t>Hepatitis B virus surface Ag [Units/volume] in Serum or Plasma by Immunoassay</t>
   </si>
   <si>
     <t>13955-0</t>
   </si>
   <si>
-    <t>Hepatitis C virus Ab [Presence] in Serum or Plasma</t>
+    <t>Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
   </si>
   <si>
     <t>47365-2</t>
   </si>
   <si>
-    <t>Hepatitis C virus Ab [Presence] in Blood</t>
+    <t>Hepatitis C virus Ab [Presence] in Serum from Donor by Immunoassay</t>
   </si>
   <si>
     <t>System URI</t>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -614,102 +614,94 @@
         <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>71</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="B25" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -225,10 +225,10 @@
     <t>Hepatitis C virus Ab [Presence] in Serum or Plasma by Immunoassay</t>
   </si>
   <si>
-    <t>47365-2</t>
-  </si>
-  <si>
-    <t>Hepatitis C virus Ab [Presence] in Serum from Donor by Immunoassay</t>
+    <t>16128-1</t>
+  </si>
+  <si>
+    <t>Hepatitis C virus Ab [Presence] in Serum</t>
   </si>
   <si>
     <t>System URI</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Core 之檢驗子集（主管機關（國健署）最小共通上傳集之 Observation.code 綁定值集，綁定強度 extensible）。僅收錄 Core 之 10 檢驗項 preferred code 及其 acceptable 變異碼；生理量測（身高/體重/腰圍/血壓）碼分屬 VS-TWHAVitalSigns、社會史（吸菸/嚼檳）碼分屬 SocialHistory profile。Core 全集（21 列）之群組見 VS-CoreUploadSet。acceptable→preferred 歸一見 ConceptMap TWHealthCheckLaboratoryMap。</t>
+    <t>【主管機關：國民健康署】Core 之檢驗子集（主管機關（國健署）最小共通上傳集之 Observation.code 綁定值集，綁定強度 extensible）。僅收錄 Core 之 10 檢驗項 preferred code 及其 acceptable 變異碼；生理量測（身高/體重/腰圍/血壓）碼分屬 VS-TWHAVitalSigns、社會史（吸菸/嚼檳）碼分屬 SocialHistory profile。Core 全集（21 列）之群組見 VS-CoreUploadSet。acceptable→preferred 歸一見 ConceptMap TWHealthCheckLaboratoryMap。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>Triglyceride [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>3048-6</t>
+  </si>
+  <si>
+    <t>Triglyceride [Mass/volume] in Serum or Plasma --fasting</t>
   </si>
   <si>
     <t>2085-9</t>
@@ -506,7 +512,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -691,18 +697,26 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>22</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>73</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="84">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -153,6 +153,12 @@
     <t>Triglyceride [Mass/volume] in Serum or Plasma --fasting</t>
   </si>
   <si>
+    <t>1644-4</t>
+  </si>
+  <si>
+    <t>Triglyceride [Mass/volume] in Serum or Plasma --12 hours fasting</t>
+  </si>
+  <si>
     <t>2085-9</t>
   </si>
   <si>
@@ -205,6 +211,24 @@
   </si>
   <si>
     <t>Protein [Presence] in Urine by Automated test strip</t>
+  </si>
+  <si>
+    <t>50561-0</t>
+  </si>
+  <si>
+    <t>Protein [Mass/volume] in Urine by Automated test strip</t>
+  </si>
+  <si>
+    <t>2887-8</t>
+  </si>
+  <si>
+    <t>Protein [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>20454-5</t>
+  </si>
+  <si>
+    <t>Protein [Presence] in Urine by Test strip</t>
   </si>
   <si>
     <t>5196-1</t>
@@ -512,7 +536,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -705,18 +729,50 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>22</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-CoreDataset.xlsx
+++ b/ValueSet-VS-CoreDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
